--- a/Result/profitability/3051.xlsx
+++ b/Result/profitability/3051.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2375</v>
+        <v>0.25125</v>
       </c>
       <c r="N2" t="n">
-        <v>29.64875</v>
+        <v>29.74</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0.01374999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>24.75125</v>
+        <v>24.505</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-3</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.43625</v>
+        <v>-0.415</v>
       </c>
       <c r="N4" t="n">
-        <v>18.52875</v>
+        <v>18.375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.48</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8</v>
+        <v>-0.7075</v>
       </c>
       <c r="N5" t="n">
-        <v>12.6025</v>
+        <v>13.40875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-2.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0375</v>
+        <v>-0.995</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2512500000000006</v>
+        <v>1.135</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.28375</v>
+        <v>-1.26625</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.59</v>
+        <v>-8.145000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4525</v>
+        <v>-1.43375</v>
       </c>
       <c r="N8" t="n">
-        <v>-12.31125</v>
+        <v>-11.46875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3051</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>559</v>
+      </c>
+      <c r="D75" t="n">
+        <v>351</v>
+      </c>
+      <c r="E75" t="n">
+        <v>208</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>118</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>128</v>
+      </c>
+      <c r="K75" t="n">
+        <v>99</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.05875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.739999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2210560839619546</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.449999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2095516569200779</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
